--- a/hairdresser_forms/014_hair_salon_feedback_form--hairdresser_forms.xlsx
+++ b/hairdresser_forms/014_hair_salon_feedback_form--hairdresser_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1106,7 +1106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -1275,29 +1275,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>service_quality</t>
+          <t>staff_quality</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Service Quality</t>
+          <t>Staff Quality</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>improvement_area_choices</t>
+          <t>service_quality_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>staff_quality</t>
+          <t>haircut</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Staff Quality</t>
+          <t>Haircut</t>
         </is>
       </c>
     </row>
@@ -1309,12 +1309,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>haircut</t>
+          <t>color</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Haircut</t>
+          <t>Color</t>
         </is>
       </c>
     </row>
@@ -1326,12 +1326,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>color</t>
+          <t>style</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Color</t>
+          <t>Style</t>
         </is>
       </c>
     </row>
@@ -1343,29 +1343,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>style</t>
+          <t>makeup</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Style</t>
+          <t>Makeup</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>service_quality_choices</t>
+          <t>staff_rating_area_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>makeup</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Makeup</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
@@ -1377,12 +1377,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>very_good</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Very Good</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1394,12 +1394,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1411,27 +1411,10 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>bad</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>staff_rating_area_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>bad</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
         <is>
           <t>Bad</t>
         </is>
